--- a/backend/calendar_files/campaign_data.xlsx
+++ b/backend/calendar_files/campaign_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmed Mohamed\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects-new\ChatBot-Integration\backend\calendar_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B81001-A470-45A2-A1B0-321914D52453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50A2D85-71FC-4377-9093-85B7AF008695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/backend/calendar_files/campaign_data.xlsx
+++ b/backend/calendar_files/campaign_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects-new\ChatBot-Integration\backend\calendar_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50A2D85-71FC-4377-9093-85B7AF008695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DEBE82-1098-4A6B-9697-5E779A6D2F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Campaign Name</t>
   </si>
@@ -38,6 +38,15 @@
   </si>
   <si>
     <t>201282692075</t>
+  </si>
+  <si>
+    <t>Mohamed Rayyan</t>
+  </si>
+  <si>
+    <t>201025223892</t>
+  </si>
+  <si>
+    <t>Test chat</t>
   </si>
 </sst>
 </file>
@@ -400,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -430,6 +439,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
